--- a/docs/downloads/经营分_鲁东省区__潍坊片区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_鲁东省区__潍坊片区_2026-10-18.xlsx
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="I2" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         <v>30</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T2" t="n">
         <v>20</v>
@@ -775,17 +775,17 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>7598674335619876864</t>
+          <t>7612774687734499334</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店（潍坊临朐店）</t>
+          <t>维也纳国际酒店(潍坊高新区兴茂科技产业园旗舰店)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>白玉兰酒店(潍坊临朐店)</t>
+          <t>维也纳国际酒店(潍坊高新区旗舰店)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>30</v>
       </c>
       <c r="Q3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R3" t="n">
         <v>30</v>
@@ -863,17 +863,17 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>7612774687734499334</t>
+          <t>7598674335619876864</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(潍坊高新区兴茂科技产业园旗舰店)</t>
+          <t>白玉兰商务酒店（潍坊临朐店）</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(潍坊高新区旗舰店)</t>
+          <t>白玉兰酒店(潍坊临朐店)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1299,17 +1299,17 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>6874490692559702030</t>
+          <t>6601265692228454403</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0寿光万达广场店)</t>
+          <t>希岸.轻雅酒店（青州古城店）</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>维也纳酒店(5.0寿光万达广场店)</t>
+          <t>希岸·轻雅酒店(潍坊青州古城宋城店)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1318,14 +1318,14 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1335,7 +1335,7 @@
         <v>10</v>
       </c>
       <c r="M9" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="N9" t="n">
         <v>30</v>
@@ -1347,7 +1347,7 @@
         <v>30</v>
       </c>
       <c r="Q9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R9" t="n">
         <v>30</v>
@@ -1387,17 +1387,17 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>6601265692228454403</t>
+          <t>7094819473206544419</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>希岸.轻雅酒店（青州古城店）</t>
+          <t>白玉兰商务酒店（青州古城店）</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>希岸·轻雅酒店(潍坊青州古城宋城店)</t>
+          <t>白玉兰(商务)酒店(潍坊青州古城衡王府路店)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1409,11 +1409,11 @@
         <v>95</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1423,13 +1423,13 @@
         <v>10</v>
       </c>
       <c r="M10" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N10" t="n">
         <v>30</v>
       </c>
       <c r="O10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P10" t="n">
         <v>30</v>
@@ -1563,17 +1563,17 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>6601142759464110094</t>
+          <t>6874490692559702030</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>维也纳酒店（青州古城店）</t>
+          <t>维也纳酒店（5.0寿光万达广场店)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>维也纳酒店(青州古城店)</t>
+          <t>维也纳酒店(5.0寿光万达广场店)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1585,11 +1585,11 @@
         <v>97</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1605,13 +1605,13 @@
         <v>30</v>
       </c>
       <c r="O12" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P12" t="n">
         <v>30</v>
       </c>
       <c r="Q12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="R12" t="n">
         <v>30</v>
@@ -1651,17 +1651,17 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>7094819473206544419</t>
+          <t>6826250171895105544</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店（青州古城店）</t>
+          <t>维也纳酒店（寿光人民广场店）</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>白玉兰(商务)酒店(潍坊青州古城衡王府路店)</t>
+          <t>维也纳酒店(寿光人民广场店)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1670,14 +1670,14 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1687,19 +1687,19 @@
         <v>10</v>
       </c>
       <c r="M13" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N13" t="n">
         <v>30</v>
       </c>
       <c r="O13" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P13" t="n">
         <v>30</v>
       </c>
       <c r="Q13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R13" t="n">
         <v>30</v>
@@ -1739,26 +1739,26 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>7606571340094539839</t>
+          <t>6601142759464110094</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>锦江之星5.1（潍坊昌邑店）</t>
+          <t>维也纳酒店（青州古城店）</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>锦江之星(潍坊昌邑店)</t>
+          <t>维也纳酒店(青州古城店)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1775,19 +1775,19 @@
         <v>10</v>
       </c>
       <c r="M14" t="n">
+        <v>22</v>
+      </c>
+      <c r="N14" t="n">
+        <v>30</v>
+      </c>
+      <c r="O14" t="n">
+        <v>30</v>
+      </c>
+      <c r="P14" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q14" t="n">
         <v>15</v>
-      </c>
-      <c r="N14" t="n">
-        <v>30</v>
-      </c>
-      <c r="O14" t="n">
-        <v>30</v>
-      </c>
-      <c r="P14" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>25</v>
       </c>
       <c r="R14" t="n">
         <v>30</v>
@@ -1827,17 +1827,17 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>6976840538032965639</t>
+          <t>7606571340094539839</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>麗枫酒店（潍坊高新区金马路店）</t>
+          <t>锦江之星5.1（潍坊昌邑店）</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>麗枫酒店(潍坊高新区金马店)</t>
+          <t>锦江之星(潍坊昌邑店)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1846,30 +1846,30 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>搭门店,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L15" t="n">
         <v>10</v>
       </c>
       <c r="M15" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N15" t="n">
         <v>30</v>
       </c>
       <c r="O15" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P15" t="n">
         <v>30</v>
@@ -1915,17 +1915,17 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>6826250171895105544</t>
+          <t>6976840538032965639</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>维也纳酒店（寿光人民广场店）</t>
+          <t>麗枫酒店（潍坊高新区金马路店）</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>维也纳酒店(寿光人民广场店)</t>
+          <t>麗枫酒店(潍坊高新区金马店)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1934,36 +1934,36 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I16" t="n">
         <v>5</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>搭门店,提质量,拿收益</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L16" t="n">
         <v>10</v>
       </c>
       <c r="M16" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="N16" t="n">
         <v>30</v>
       </c>
       <c r="O16" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P16" t="n">
         <v>30</v>
       </c>
       <c r="Q16" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R16" t="n">
         <v>30</v>
@@ -2113,7 +2113,7 @@
         <v>105</v>
       </c>
       <c r="I18" t="n">
-        <v>-5</v>
+        <v>20</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -2179,17 +2179,17 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>7229182208345393212</t>
+          <t>7081617643366516766</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（临朐万达广场店）</t>
+          <t>喆啡酒店（潍坊火车站泰华城店）</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(临朐万达广场店)</t>
+          <t>喆·啡酒店(潍坊火车站泰华城店)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2198,14 +2198,14 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>拿收益</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -2215,7 +2215,7 @@
         <v>10</v>
       </c>
       <c r="M19" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="N19" t="n">
         <v>30</v>
@@ -2227,7 +2227,7 @@
         <v>30</v>
       </c>
       <c r="Q19" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R19" t="n">
         <v>30</v>
@@ -2267,17 +2267,17 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>7081617643366516766</t>
+          <t>6683400621237880839</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>喆啡酒店（潍坊火车站泰华城店）</t>
+          <t>希岸酒店（潍坊泰华城火车站店）</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>喆·啡酒店(潍坊火车站泰华城店)</t>
+          <t>希岸酒店(潍坊泰华城火车站店)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2289,7 +2289,7 @@
         <v>110</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -2355,17 +2355,17 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>6683400621237880839</t>
+          <t>6601259847830734852</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>希岸酒店（潍坊泰华城火车站店）</t>
+          <t>维也纳国际酒店（山东潍坊高密花园街店）</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>希岸酒店(潍坊泰华城火车站店)</t>
+          <t>维也纳国际酒店(高密花园街店)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2377,11 +2377,11 @@
         <v>110</v>
       </c>
       <c r="I21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -2397,13 +2397,13 @@
         <v>30</v>
       </c>
       <c r="O21" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P21" t="n">
         <v>30</v>
       </c>
       <c r="Q21" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R21" t="n">
         <v>30</v>
@@ -2443,17 +2443,17 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>6601259847830734852</t>
+          <t>7277813763514828800</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（山东潍坊高密花园街店）</t>
+          <t>维也纳国际酒店（诸城密州路市府店）</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(高密花园街店)</t>
+          <t>维也纳国际酒店(诸城密州路市政府店)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2465,11 +2465,11 @@
         <v>110</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>拿收益</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -2485,13 +2485,13 @@
         <v>30</v>
       </c>
       <c r="O22" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P22" t="n">
         <v>30</v>
       </c>
       <c r="Q22" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R22" t="n">
         <v>30</v>
@@ -2531,17 +2531,17 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>7277813763514828800</t>
+          <t>7333827461253171237</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（诸城密州路市府店）</t>
+          <t>维也纳酒店（5.0潍坊坊子店）</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(诸城密州路市政府店)</t>
+          <t>维也纳酒店(潍坊坊子店)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2553,7 +2553,7 @@
         <v>110</v>
       </c>
       <c r="I23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -2619,17 +2619,17 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>7333827461253171237</t>
+          <t>7625501294187038772</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0潍坊坊子店）</t>
+          <t>锦江之星（青州古城博物馆店）</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>维也纳酒店(潍坊坊子店)</t>
+          <t>锦江之星(青州古城博物馆店)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -2655,7 +2655,7 @@
         <v>10</v>
       </c>
       <c r="M24" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N24" t="n">
         <v>30</v>
@@ -2667,7 +2667,7 @@
         <v>30</v>
       </c>
       <c r="Q24" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R24" t="n">
         <v>30</v>
@@ -2707,17 +2707,17 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>7625501294187038772</t>
+          <t>7229182208345393212</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>锦江之星（青州古城博物馆店）</t>
+          <t>维也纳国际酒店（临朐万达广场店）</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>锦江之星(青州古城博物馆店)</t>
+          <t>维也纳国际酒店(临朐万达广场店)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2726,14 +2726,14 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -2743,7 +2743,7 @@
         <v>10</v>
       </c>
       <c r="M25" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N25" t="n">
         <v>30</v>
@@ -2755,7 +2755,7 @@
         <v>30</v>
       </c>
       <c r="Q25" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="R25" t="n">
         <v>30</v>
@@ -2795,17 +2795,17 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>6824371701640382468</t>
+          <t>6601191648141510669</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>维也纳3好酒店（山东潍坊临朐店）</t>
+          <t>维也纳国际酒店（青州古城店）</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>维也纳3好酒店(山东潍坊临朐店)</t>
+          <t>维也纳国际酒店(青州店)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2814,18 +2814,18 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>搭门店,拿收益</t>
+          <t>提质量</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L26" t="n">
         <v>10</v>
@@ -2837,13 +2837,13 @@
         <v>30</v>
       </c>
       <c r="O26" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P26" t="n">
         <v>30</v>
       </c>
       <c r="Q26" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="R26" t="n">
         <v>30</v>
@@ -2883,17 +2883,17 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>6601191648141510669</t>
+          <t>6952255158147352616</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（青州古城店）</t>
+          <t>麗枫酒店（潍坊诸城恐龙公园汽车站店）</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(青州店)</t>
+          <t>麗枫酒店(潍坊诸城恐龙公园店)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2905,11 +2905,11 @@
         <v>115</v>
       </c>
       <c r="I27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>提质量</t>
+          <t>拿收益</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2925,13 +2925,13 @@
         <v>30</v>
       </c>
       <c r="O27" t="n">
+        <v>30</v>
+      </c>
+      <c r="P27" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q27" t="n">
         <v>25</v>
-      </c>
-      <c r="P27" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>30</v>
       </c>
       <c r="R27" t="n">
         <v>30</v>
@@ -2971,37 +2971,37 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>6952255158147352616</t>
+          <t>6824371701640382468</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>麗枫酒店（潍坊诸城恐龙公园汽车站店）</t>
+          <t>维也纳3好酒店（山东潍坊临朐店）</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>麗枫酒店(潍坊诸城恐龙公园店)</t>
+          <t>维也纳3好酒店(山东潍坊临朐店)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>拿收益</t>
+          <t>搭门店</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L28" t="n">
         <v>10</v>
@@ -3019,7 +3019,7 @@
         <v>30</v>
       </c>
       <c r="Q28" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="R28" t="n">
         <v>30</v>
